--- a/Zeitplan.xlsx
+++ b/Zeitplan.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Planung</t>
   </si>
@@ -82,21 +82,6 @@
   </si>
   <si>
     <t>Präsentation</t>
-  </si>
-  <si>
-    <t>knoten anlegen für punkte 1-4</t>
-  </si>
-  <si>
-    <t>knoten anlegen5-6</t>
-  </si>
-  <si>
-    <t>knoten anlegen für 7</t>
-  </si>
-  <si>
-    <t>knoten anlegen für 8&amp;9</t>
-  </si>
-  <si>
-    <t>launch datei anlegen</t>
   </si>
   <si>
     <t>Kalenderwoche:</t>
@@ -165,7 +150,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -236,9 +221,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -249,12 +231,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -275,6 +251,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -597,23 +582,23 @@
   <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="18">
+      <c r="A1" s="15">
         <f ca="1">TODAY()</f>
-        <v>45671</v>
-      </c>
-      <c r="B1" s="18" t="s">
-        <v>28</v>
+        <v>45710</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>23</v>
       </c>
       <c r="C1">
         <f ca="1">WEEKNUM(A1,2)</f>
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -624,58 +609,58 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
       <c r="F2" s="4"/>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="22"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="21" t="s">
+      <c r="H2" s="19"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="18" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="19">
+        <v>22</v>
+      </c>
+      <c r="C3" s="16">
         <v>2</v>
       </c>
       <c r="D3" s="5">
         <v>3</v>
       </c>
-      <c r="E3" s="19">
+      <c r="E3" s="16">
         <v>4</v>
       </c>
       <c r="F3" s="6">
         <v>5</v>
       </c>
-      <c r="G3" s="19">
+      <c r="G3" s="16">
         <v>6</v>
       </c>
       <c r="H3" s="5">
         <v>7</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="17">
         <v>8</v>
       </c>
       <c r="J3" s="5">
         <v>9</v>
       </c>
-      <c r="K3" s="19">
+      <c r="K3" s="16">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="21" t="s">
         <v>20</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="7"/>
+      <c r="C4" s="8"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
       <c r="F4" s="4"/>
@@ -686,11 +671,11 @@
       <c r="K4" s="3"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="24"/>
+      <c r="A5" s="21"/>
       <c r="B5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="7"/>
+      <c r="C5" s="8"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="4"/>
@@ -701,12 +686,12 @@
       <c r="K5" s="3"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
+      <c r="A6" s="21"/>
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="9"/>
       <c r="G6" s="8"/>
@@ -716,18 +701,18 @@
       <c r="K6" s="3"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
+      <c r="A7" s="21"/>
       <c r="B7" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="12"/>
       <c r="H7" s="8"/>
       <c r="I7" s="9"/>
-      <c r="J7" s="3"/>
+      <c r="J7" s="8"/>
       <c r="K7" s="3"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
@@ -741,11 +726,11 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="8"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="24" t="s">
+      <c r="A9" s="21" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -762,7 +747,7 @@
       <c r="K9" s="3"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="24"/>
+      <c r="A10" s="21"/>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
@@ -777,7 +762,7 @@
       <c r="K10" s="3"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="24"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="1" t="s">
         <v>9</v>
       </c>
@@ -792,14 +777,14 @@
       <c r="K11" s="3"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="24"/>
+      <c r="A12" s="21"/>
       <c r="B12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="7"/>
-      <c r="F12" s="11"/>
+      <c r="F12" s="10"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -807,52 +792,52 @@
       <c r="K12" s="3"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="24"/>
+      <c r="A13" s="21"/>
       <c r="B13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="13"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="11"/>
+      <c r="G13" s="12"/>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="24"/>
+      <c r="A14" s="21"/>
       <c r="B14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="12"/>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="24"/>
+      <c r="A15" s="21"/>
       <c r="B15" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="14"/>
+      <c r="F15" s="13"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="11"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="10"/>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="21" t="s">
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
@@ -862,14 +847,14 @@
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="4"/>
-      <c r="G16" s="7"/>
+      <c r="G16" s="12"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="4"/>
+      <c r="I16" s="13"/>
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="24"/>
+      <c r="A17" s="21"/>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
@@ -878,13 +863,13 @@
       <c r="E17" s="3"/>
       <c r="F17" s="4"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="14"/>
+      <c r="H17" s="23"/>
+      <c r="I17" s="24"/>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="24"/>
+      <c r="A18" s="21"/>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
@@ -892,9 +877,9 @@
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="4"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="16"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+      <c r="I18" s="24"/>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
     </row>
@@ -910,29 +895,19 @@
       <c r="K19" s="3"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B20" s="17" t="s">
-        <v>22</v>
-      </c>
+      <c r="B20" s="14"/>
     </row>
     <row r="21" spans="1:11" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B21" s="17" t="s">
-        <v>23</v>
-      </c>
+      <c r="B21" s="14"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
-        <v>24</v>
-      </c>
+      <c r="B22" s="14"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B23" s="17" t="s">
-        <v>25</v>
-      </c>
+      <c r="B23" s="14"/>
     </row>
     <row r="24" spans="1:11" ht="14.45" x14ac:dyDescent="0.3">
-      <c r="B24" s="17" t="s">
-        <v>26</v>
-      </c>
+      <c r="B24" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
